--- a/docs/Kエナジー_DD/チェックシート/PX案件チェックシート_1748_一関・東山.xlsx
+++ b/docs/Kエナジー_DD/チェックシート/PX案件チェックシート_1748_一関・東山.xlsx
@@ -2973,7 +2973,7 @@
       <c r="E17" s="9" t="inlineStr"/>
       <c r="F17" s="9" t="inlineStr">
         <is>
-          <t>輸送可否（可／要対策／不可）と必要対策。 / ①県道から約760mの進入ルート確認 ②造成計画の概算 ③東山変電所で接続検討を申込</t>
+          <t>輸送可否（可／要対策／不可）と必要対策。 / ①東山変電所の上位系（水沢275kV）の増強リスクを電力会社へ事前相談 ②県道から約760mの進入ルート確認 ③造成計画の概算</t>
         </is>
       </c>
     </row>
